--- a/data/trans_dic/IP09B02-Clase-trans_dic.xlsx
+++ b/data/trans_dic/IP09B02-Clase-trans_dic.xlsx
@@ -7,7 +7,8 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Variables dicotomizadas" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Porcentajes" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Totales" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -526,7 +527,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores según si dicha enfermedad o dolencia continuada le ha afectado para realizar actividades como pasear, ir al cine, hacer deporte, etc</t>
+          <t>Menores según si dicha enfermedad o dolencia continuada le ha afectado para realizar actividades como pasear, ir al cine, hacer deporte, etc (tasa de respuesta: 98,79%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -716,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>38,5; 87,2</t>
+          <t>39,66; 87,42</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>29,4; 89,67</t>
+          <t>27,74; 88,64</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>9,63; 77,96</t>
+          <t>11,14; 85,01</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>55,22; 95,38</t>
+          <t>58,22; 95,03</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>63,58; 100,0</t>
+          <t>64,05; 100,0</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>37,56; 91,32</t>
+          <t>37,66; 91,18</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>17,62; 72,7</t>
+          <t>17,44; 73,05</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>28,47; 74,24</t>
+          <t>28,7; 74,39</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>59,4; 90,11</t>
+          <t>60,07; 90,39</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>43,05; 85,0</t>
+          <t>43,6; 85,61</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>22,67; 66,76</t>
+          <t>22,65; 66,4</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>47,99; 78,73</t>
+          <t>47,69; 78,57</t>
         </is>
       </c>
     </row>
@@ -856,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>32,35; 91,8</t>
+          <t>35,16; 91,76</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>50,34; 100,0</t>
+          <t>51,26; 100,0</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 79,19</t>
+          <t>0,0; 100,0</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>41,67; 93,12</t>
+          <t>45,11; 92,76</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>37,01; 90,84</t>
+          <t>37,75; 91,68</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>20,78; 74,72</t>
+          <t>22,6; 75,74</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>22,11; 75,46</t>
+          <t>21,04; 74,5</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>56,21; 95,4</t>
+          <t>55,62; 95,9</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>47,26; 85,96</t>
+          <t>48,93; 85,84</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>45,71; 82,6</t>
+          <t>45,13; 82,9</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>18,5; 65,6</t>
+          <t>17,78; 65,13</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>60,66; 91,57</t>
+          <t>62,31; 93,05</t>
         </is>
       </c>
     </row>
@@ -996,12 +997,12 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>73,58; 100</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>17,51; 69,05</t>
+          <t>15,88; 73,59</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
@@ -1011,47 +1012,47 @@
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>63,75; 100</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>70,78; 100,0</t>
+          <t>70,66; 100,0</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>46,17; 89,1</t>
+          <t>47,42; 89,36</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>11,37; 79,22</t>
+          <t>11,26; 78,83</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>33,41; 93,63</t>
+          <t>38,08; 94,17</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>76,78; 100,0</t>
+          <t>73,63; 100,0</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>39,98; 76,51</t>
+          <t>41,23; 78,64</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>15,3; 68,85</t>
+          <t>19,1; 70,55</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>45,52; 95,46</t>
+          <t>46,72; 95,12</t>
         </is>
       </c>
     </row>
@@ -1136,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>41,53; 77,67</t>
+          <t>40,82; 78,71</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>54,43; 79,8</t>
+          <t>53,39; 80,07</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>43,32; 79,4</t>
+          <t>42,77; 81,12</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>61,48; 94,36</t>
+          <t>61,72; 93,7</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>70,0; 96,63</t>
+          <t>69,69; 96,61</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>48,92; 74,87</t>
+          <t>46,83; 73,79</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>57,37; 100,0</t>
+          <t>57,27; 100,0</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>59,21; 85,48</t>
+          <t>59,73; 86,29</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>61,86; 84,43</t>
+          <t>61,9; 85,1</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>55,17; 72,91</t>
+          <t>54,76; 73,36</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>56,71; 84,49</t>
+          <t>56,65; 83,91</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>65,93; 87,25</t>
+          <t>64,33; 86,01</t>
         </is>
       </c>
     </row>
@@ -1276,62 +1277,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>60,59; 100,0</t>
+          <t>58,64; 100,0</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>43,75; 81,14</t>
+          <t>45,23; 81,73</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>24,84; 69,38</t>
+          <t>26,66; 69,09</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>66,7; 100,0</t>
+          <t>63,75; 100,0</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>48,9; 87,2</t>
+          <t>48,82; 87,22</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>39,88; 75,36</t>
+          <t>40,81; 77,81</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>33,55; 81,69</t>
+          <t>28,85; 80,53</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>77,91; 100,0</t>
+          <t>78,24; 100,0</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>62,16; 89,06</t>
+          <t>61,08; 89,57</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>47,07; 73,18</t>
+          <t>47,83; 73,41</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>35,44; 68,52</t>
+          <t>34,81; 68,41</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>80,15; 97,9</t>
+          <t>81,68; 98,5</t>
         </is>
       </c>
     </row>
@@ -1416,62 +1417,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>26,0; 100,0</t>
+          <t>23,75; 100,0</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 74,92</t>
+          <t>0,0; 74,71</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 83,7</t>
+          <t>0,0; 100,0</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>19,03; 100,0</t>
+          <t>9,2; 100,0</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>56,34; 100,0</t>
+          <t>55,53; 100,0</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>40,0; 100,0</t>
+          <t>39,48; 100,0</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>11,67; 72,35</t>
+          <t>12,54; 72,61</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>9,0; 78,32</t>
+          <t>8,48; 73,44</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>57,11; 94,7</t>
+          <t>57,29; 94,76</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>31,73; 81,06</t>
+          <t>31,18; 81,83</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>14,64; 65,68</t>
+          <t>14,52; 65,23</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>19,9; 74,03</t>
+          <t>19,8; 72,45</t>
         </is>
       </c>
     </row>
@@ -1556,62 +1557,62 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>60,8; 82,02</t>
+          <t>61,51; 82,15</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>52,75; 70,14</t>
+          <t>53,87; 71,23</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>36,08; 61,38</t>
+          <t>37,91; 60,79</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>70,22; 88,39</t>
+          <t>70,86; 89,1</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>73,35; 87,85</t>
+          <t>73,48; 87,8</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>54,71; 71,19</t>
+          <t>53,97; 71,08</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>44,64; 67,61</t>
+          <t>44,81; 66,87</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>66,27; 83,59</t>
+          <t>65,69; 83,48</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>72,37; 84,35</t>
+          <t>72,16; 83,83</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>56,96; 68,89</t>
+          <t>57,6; 69,62</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>43,76; 60,94</t>
+          <t>44,24; 61,56</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>70,74; 83,83</t>
+          <t>71,04; 83,82</t>
         </is>
       </c>
     </row>
@@ -1638,4 +1639,1622 @@
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:N25"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
+    <col width="14" customWidth="1" min="7" max="7"/>
+    <col width="14" customWidth="1" min="8" max="8"/>
+    <col width="14" customWidth="1" min="9" max="9"/>
+    <col width="14" customWidth="1" min="10" max="10"/>
+    <col width="14" customWidth="1" min="11" max="11"/>
+    <col width="14" customWidth="1" min="12" max="12"/>
+    <col width="14" customWidth="1" min="13" max="13"/>
+    <col width="14" customWidth="1" min="14" max="14"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Menores según si dicha enfermedad o dolencia continuada le ha afectado para realizar actividades como pasear, ir al cine, hacer deporte, etc (tasa de respuesta: 98,79%)</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="n"/>
+      <c r="C1" s="3" t="inlineStr">
+        <is>
+          <t>Niña</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="n"/>
+      <c r="E1" s="3" t="n"/>
+      <c r="F1" s="3" t="n"/>
+      <c r="G1" s="3" t="inlineStr">
+        <is>
+          <t>Niño</t>
+        </is>
+      </c>
+      <c r="H1" s="3" t="n"/>
+      <c r="I1" s="3" t="n"/>
+      <c r="J1" s="3" t="n"/>
+      <c r="K1" s="3" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="L1" s="3" t="n"/>
+      <c r="M1" s="3" t="n"/>
+      <c r="N1" s="3" t="n"/>
+    </row>
+    <row r="2">
+      <c r="A2" s="4" t="n"/>
+      <c r="B2" s="2" t="n"/>
+      <c r="C2" s="3" t="inlineStr">
+        <is>
+          <t>2007</t>
+        </is>
+      </c>
+      <c r="D2" s="3" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="E2" s="3" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="F2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="G2" s="3" t="inlineStr">
+        <is>
+          <t>2007</t>
+        </is>
+      </c>
+      <c r="H2" s="3" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="I2" s="3" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="J2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="K2" s="3" t="inlineStr">
+        <is>
+          <t>2007</t>
+        </is>
+      </c>
+      <c r="L2" s="3" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="M2" s="3" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="N2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" hidden="1">
+      <c r="A3" s="4" t="n"/>
+      <c r="B3" s="2" t="n"/>
+      <c r="C3" s="2" t="n"/>
+      <c r="D3" s="2" t="n"/>
+      <c r="E3" s="2" t="n"/>
+      <c r="F3" s="2" t="n"/>
+      <c r="G3" s="2" t="n"/>
+      <c r="H3" s="2" t="n"/>
+      <c r="I3" s="2" t="n"/>
+      <c r="J3" s="2" t="n"/>
+      <c r="K3" s="2" t="n"/>
+      <c r="L3" s="2" t="n"/>
+      <c r="M3" s="2" t="n"/>
+      <c r="N3" s="2" t="n"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="1" t="inlineStr">
+        <is>
+          <t>Grupo I y II</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="K4" s="2" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="1" t="n"/>
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>6521</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>4075</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>2297</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>8706</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>10088</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>5396</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>3271</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
+          <t>7372</t>
+        </is>
+      </c>
+      <c r="K5" s="2" t="inlineStr">
+        <is>
+          <t>16609</t>
+        </is>
+      </c>
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>9471</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>5568</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
+        <is>
+          <t>16079</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="n"/>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>3883; 8557</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>1887; 6030</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>597; 4555</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>6185; 10095</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>7349; 11474</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>2822; 6833</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>1304; 5461</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
+          <t>4093; 10612</t>
+        </is>
+      </c>
+      <c r="K6" s="2" t="inlineStr">
+        <is>
+          <t>12773; 19221</t>
+        </is>
+      </c>
+      <c r="L6" s="2" t="inlineStr">
+        <is>
+          <t>6233; 12238</t>
+        </is>
+      </c>
+      <c r="M6" s="2" t="inlineStr">
+        <is>
+          <t>2907; 8521</t>
+        </is>
+      </c>
+      <c r="N6" s="2" t="inlineStr">
+        <is>
+          <t>11870; 19554</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
+        <is>
+          <t>Grupo III</t>
+        </is>
+      </c>
+      <c r="B7" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="K7" s="2" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="n"/>
+      <c r="B8" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>5451</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>7076</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>724</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>6116</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>5922</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>4006</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>3891</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
+          <t>9295</t>
+        </is>
+      </c>
+      <c r="K8" s="2" t="inlineStr">
+        <is>
+          <t>11373</t>
+        </is>
+      </c>
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>11082</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>4614</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
+        <is>
+          <t>15411</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="n"/>
+      <c r="B9" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>2708; 7069</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>4344; 8475</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>0; 2567</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>3699; 7607</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>3280; 7964</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>1877; 6290</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>1795; 6356</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
+          <t>6253; 10781</t>
+        </is>
+      </c>
+      <c r="K9" s="2" t="inlineStr">
+        <is>
+          <t>8020; 14071</t>
+        </is>
+      </c>
+      <c r="L9" s="2" t="inlineStr">
+        <is>
+          <t>7573; 13910</t>
+        </is>
+      </c>
+      <c r="M9" s="2" t="inlineStr">
+        <is>
+          <t>1973; 7228</t>
+        </is>
+      </c>
+      <c r="N9" s="2" t="inlineStr">
+        <is>
+          <t>12116; 18093</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>Grupo IV y V</t>
+        </is>
+      </c>
+      <c r="B10" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="K10" s="2" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="n"/>
+      <c r="B11" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>3842</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>3415</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>1234</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>2560</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>12566</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>8646</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>2588</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
+          <t>5489</t>
+        </is>
+      </c>
+      <c r="K11" s="2" t="inlineStr">
+        <is>
+          <t>16409</t>
+        </is>
+      </c>
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>12061</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>3822</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
+        <is>
+          <t>8050</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="n"/>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>1299; 6021</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>0; 2723</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>9801; 13871</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>5759; 10853</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>647; 4528</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
+          <t>2958; 7315</t>
+        </is>
+      </c>
+      <c r="K12" s="2" t="inlineStr">
+        <is>
+          <t>13043; 17714</t>
+        </is>
+      </c>
+      <c r="L12" s="2" t="inlineStr">
+        <is>
+          <t>8380; 15985</t>
+        </is>
+      </c>
+      <c r="M12" s="2" t="inlineStr">
+        <is>
+          <t>1732; 6397</t>
+        </is>
+      </c>
+      <c r="N12" s="2" t="inlineStr">
+        <is>
+          <t>4826; 9825</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>Grupo VI</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>33</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>31</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
+          <t>29</t>
+        </is>
+      </c>
+      <c r="K13" s="2" t="inlineStr">
+        <is>
+          <t>42</t>
+        </is>
+      </c>
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>64</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>29</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
+        <is>
+          <t>53</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="n"/>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>10620</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>22875</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>10297</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>20226</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>17350</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>22903</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>9343</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
+          <t>23401</t>
+        </is>
+      </c>
+      <c r="K14" s="2" t="inlineStr">
+        <is>
+          <t>27969</t>
+        </is>
+      </c>
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>45778</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>19640</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
+        <is>
+          <t>43628</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="n"/>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>7107; 13704</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>18061; 27087</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>7020; 13314</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>15463; 23475</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>13954; 19345</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>17390; 27399</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>6272; 10953</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
+          <t>18652; 26946</t>
+        </is>
+      </c>
+      <c r="K15" s="2" t="inlineStr">
+        <is>
+          <t>23170; 31855</t>
+        </is>
+      </c>
+      <c r="L15" s="2" t="inlineStr">
+        <is>
+          <t>38859; 52058</t>
+        </is>
+      </c>
+      <c r="M15" s="2" t="inlineStr">
+        <is>
+          <t>15501; 22962</t>
+        </is>
+      </c>
+      <c r="N15" s="2" t="inlineStr">
+        <is>
+          <t>36208; 48409</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
+        <is>
+          <t>Grupo VII</t>
+        </is>
+      </c>
+      <c r="B16" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C16" s="2" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="K16" s="2" t="inlineStr">
+        <is>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>34</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
+        <is>
+          <t>35</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="n"/>
+      <c r="B17" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C17" s="2" t="inlineStr">
+        <is>
+          <t>8016</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>10996</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>6594</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>11507</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>10863</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>13457</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>5786</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
+          <t>24766</t>
+        </is>
+      </c>
+      <c r="K17" s="2" t="inlineStr">
+        <is>
+          <t>18879</t>
+        </is>
+      </c>
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>24453</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>12380</t>
+        </is>
+      </c>
+      <c r="N17" s="2" t="inlineStr">
+        <is>
+          <t>36272</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="n"/>
+      <c r="B18" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C18" s="2" t="inlineStr">
+        <is>
+          <t>5130; 8749</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>7855; 14194</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>3666; 9500</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>8300; 13020</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>7572; 13526</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>9236; 17612</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>2858; 7980</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
+          <t>20731; 26496</t>
+        </is>
+      </c>
+      <c r="K18" s="2" t="inlineStr">
+        <is>
+          <t>14818; 21727</t>
+        </is>
+      </c>
+      <c r="L18" s="2" t="inlineStr">
+        <is>
+          <t>19134; 29363</t>
+        </is>
+      </c>
+      <c r="M18" s="2" t="inlineStr">
+        <is>
+          <t>8235; 16184</t>
+        </is>
+      </c>
+      <c r="N18" s="2" t="inlineStr">
+        <is>
+          <t>32276; 38922</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="1" t="inlineStr">
+        <is>
+          <t>No ha trabajado</t>
+        </is>
+      </c>
+      <c r="B19" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C19" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="H19" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="I19" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J19" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="K19" s="2" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="L19" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="M19" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="N19" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="1" t="n"/>
+      <c r="B20" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C20" s="2" t="inlineStr">
+        <is>
+          <t>3640</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>1498</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>792</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>2425</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
+          <t>6548</t>
+        </is>
+      </c>
+      <c r="H20" s="2" t="inlineStr">
+        <is>
+          <t>5021</t>
+        </is>
+      </c>
+      <c r="I20" s="2" t="inlineStr">
+        <is>
+          <t>2917</t>
+        </is>
+      </c>
+      <c r="J20" s="2" t="inlineStr">
+        <is>
+          <t>2172</t>
+        </is>
+      </c>
+      <c r="K20" s="2" t="inlineStr">
+        <is>
+          <t>10187</t>
+        </is>
+      </c>
+      <c r="L20" s="2" t="inlineStr">
+        <is>
+          <t>6520</t>
+        </is>
+      </c>
+      <c r="M20" s="2" t="inlineStr">
+        <is>
+          <t>3709</t>
+        </is>
+      </c>
+      <c r="N20" s="2" t="inlineStr">
+        <is>
+          <t>4598</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="1" t="n"/>
+      <c r="B21" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C21" s="2" t="inlineStr">
+        <is>
+          <t>1099; 4626</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>0; 3687</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="inlineStr">
+        <is>
+          <t>0; 2895</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>376; 4089</t>
+        </is>
+      </c>
+      <c r="G21" s="2" t="inlineStr">
+        <is>
+          <t>4400; 7924</t>
+        </is>
+      </c>
+      <c r="H21" s="2" t="inlineStr">
+        <is>
+          <t>2512; 6361</t>
+        </is>
+      </c>
+      <c r="I21" s="2" t="inlineStr">
+        <is>
+          <t>897; 5192</t>
+        </is>
+      </c>
+      <c r="J21" s="2" t="inlineStr">
+        <is>
+          <t>479; 4142</t>
+        </is>
+      </c>
+      <c r="K21" s="2" t="inlineStr">
+        <is>
+          <t>7190; 11893</t>
+        </is>
+      </c>
+      <c r="L21" s="2" t="inlineStr">
+        <is>
+          <t>3522; 9244</t>
+        </is>
+      </c>
+      <c r="M21" s="2" t="inlineStr">
+        <is>
+          <t>1458; 6553</t>
+        </is>
+      </c>
+      <c r="N21" s="2" t="inlineStr">
+        <is>
+          <t>1926; 7049</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="1" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="B22" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C22" s="2" t="inlineStr">
+        <is>
+          <t>57</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>72</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>33</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
+          <t>71</t>
+        </is>
+      </c>
+      <c r="G22" s="2" t="inlineStr">
+        <is>
+          <t>94</t>
+        </is>
+      </c>
+      <c r="H22" s="2" t="inlineStr">
+        <is>
+          <t>84</t>
+        </is>
+      </c>
+      <c r="I22" s="2" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="J22" s="2" t="inlineStr">
+        <is>
+          <t>78</t>
+        </is>
+      </c>
+      <c r="K22" s="2" t="inlineStr">
+        <is>
+          <t>151</t>
+        </is>
+      </c>
+      <c r="L22" s="2" t="inlineStr">
+        <is>
+          <t>156</t>
+        </is>
+      </c>
+      <c r="M22" s="2" t="inlineStr">
+        <is>
+          <t>73</t>
+        </is>
+      </c>
+      <c r="N22" s="2" t="inlineStr">
+        <is>
+          <t>149</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="1" t="n"/>
+      <c r="B23" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C23" s="2" t="inlineStr">
+        <is>
+          <t>38088</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>49935</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>21937</t>
+        </is>
+      </c>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
+          <t>51540</t>
+        </is>
+      </c>
+      <c r="G23" s="2" t="inlineStr">
+        <is>
+          <t>63337</t>
+        </is>
+      </c>
+      <c r="H23" s="2" t="inlineStr">
+        <is>
+          <t>59430</t>
+        </is>
+      </c>
+      <c r="I23" s="2" t="inlineStr">
+        <is>
+          <t>27796</t>
+        </is>
+      </c>
+      <c r="J23" s="2" t="inlineStr">
+        <is>
+          <t>72496</t>
+        </is>
+      </c>
+      <c r="K23" s="2" t="inlineStr">
+        <is>
+          <t>101426</t>
+        </is>
+      </c>
+      <c r="L23" s="2" t="inlineStr">
+        <is>
+          <t>109364</t>
+        </is>
+      </c>
+      <c r="M23" s="2" t="inlineStr">
+        <is>
+          <t>49733</t>
+        </is>
+      </c>
+      <c r="N23" s="2" t="inlineStr">
+        <is>
+          <t>124037</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="1" t="n"/>
+      <c r="B24" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C24" s="2" t="inlineStr">
+        <is>
+          <t>32059; 42814</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>42876; 56691</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
+          <t>16795; 26932</t>
+        </is>
+      </c>
+      <c r="F24" s="2" t="inlineStr">
+        <is>
+          <t>45028; 56624</t>
+        </is>
+      </c>
+      <c r="G24" s="2" t="inlineStr">
+        <is>
+          <t>56938; 68040</t>
+        </is>
+      </c>
+      <c r="H24" s="2" t="inlineStr">
+        <is>
+          <t>50773; 66862</t>
+        </is>
+      </c>
+      <c r="I24" s="2" t="inlineStr">
+        <is>
+          <t>22301; 33279</t>
+        </is>
+      </c>
+      <c r="J24" s="2" t="inlineStr">
+        <is>
+          <t>63486; 80674</t>
+        </is>
+      </c>
+      <c r="K24" s="2" t="inlineStr">
+        <is>
+          <t>93525; 108655</t>
+        </is>
+      </c>
+      <c r="L24" s="2" t="inlineStr">
+        <is>
+          <t>100024; 120897</t>
+        </is>
+      </c>
+      <c r="M24" s="2" t="inlineStr">
+        <is>
+          <t>41615; 57911</t>
+        </is>
+      </c>
+      <c r="N24" s="2" t="inlineStr">
+        <is>
+          <t>113803; 134268</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>Fuente: Encuesta Andaluza de Salud (menores)</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="11">
+    <mergeCell ref="A7:A9"/>
+    <mergeCell ref="A4:A6"/>
+    <mergeCell ref="A16:A18"/>
+    <mergeCell ref="A10:A12"/>
+    <mergeCell ref="A19:A21"/>
+    <mergeCell ref="A1:B2"/>
+    <mergeCell ref="C1:F1"/>
+    <mergeCell ref="G1:J1"/>
+    <mergeCell ref="K1:N1"/>
+    <mergeCell ref="A22:A24"/>
+    <mergeCell ref="A13:A15"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/data/trans_dic/IP09B02-Clase-trans_dic.xlsx
+++ b/data/trans_dic/IP09B02-Clase-trans_dic.xlsx
@@ -527,7 +527,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores según si dicha enfermedad o dolencia continuada le ha afectado para realizar actividades como pasear, ir al cine, hacer deporte, etc (tasa de respuesta: 98,79%)</t>
+          <t>Menores según si dicha enfermedad o dolencia continuada le ha afectado para realizar actividades de ocio como pasear, ir al cine, hacer deporte, etc (tasa de respuesta: 98,79%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>39,66; 87,42</t>
+          <t>40,62; 88,49</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>27,74; 88,64</t>
+          <t>29,55; 90,27</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>11,14; 85,01</t>
+          <t>10,15; 77,69</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>58,22; 95,03</t>
+          <t>58,5; 94,71</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>64,05; 100,0</t>
+          <t>63,78; 100,0</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>37,66; 91,18</t>
+          <t>42,56; 91,49</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>17,44; 73,05</t>
+          <t>16,81; 72,82</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>28,7; 74,39</t>
+          <t>29,05; 75,18</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>60,07; 90,39</t>
+          <t>61,6; 90,36</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>43,6; 85,61</t>
+          <t>42,78; 85,48</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>22,65; 66,4</t>
+          <t>21,3; 66,36</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>47,69; 78,57</t>
+          <t>47,79; 78,64</t>
         </is>
       </c>
     </row>
@@ -857,12 +857,12 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>35,16; 91,76</t>
+          <t>31,16; 91,76</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>51,26; 100,0</t>
+          <t>53,19; 100,0</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
@@ -872,47 +872,47 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>45,11; 92,76</t>
+          <t>42,64; 92,78</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>37,75; 91,68</t>
+          <t>38,04; 91,92</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>22,6; 75,74</t>
+          <t>22,41; 75,39</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>21,04; 74,5</t>
+          <t>20,52; 76,23</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>55,62; 95,9</t>
+          <t>55,38; 95,71</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>48,93; 85,84</t>
+          <t>48,4; 86,01</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>45,13; 82,9</t>
+          <t>45,41; 82,93</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>17,78; 65,13</t>
+          <t>17,71; 65,38</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>62,31; 93,05</t>
+          <t>58,12; 91,6</t>
         </is>
       </c>
     </row>
@@ -1002,7 +1002,7 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>15,88; 73,59</t>
+          <t>15,16; 74,71</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
@@ -1017,42 +1017,42 @@
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>70,66; 100,0</t>
+          <t>70,98; 100,0</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>47,42; 89,36</t>
+          <t>43,95; 88,58</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>11,26; 78,83</t>
+          <t>11,34; 78,51</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>38,08; 94,17</t>
+          <t>38,69; 93,9</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>73,63; 100,0</t>
+          <t>74,0; 100,0</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>41,23; 78,64</t>
+          <t>39,18; 77,03</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>19,1; 70,55</t>
+          <t>19,7; 70,8</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>46,72; 95,12</t>
+          <t>49,7; 95,59</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>40,82; 78,71</t>
+          <t>40,93; 77,07</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>53,39; 80,07</t>
+          <t>53,89; 79,2</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>42,77; 81,12</t>
+          <t>41,28; 79,18</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>61,72; 93,7</t>
+          <t>62,29; 93,21</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>69,69; 96,61</t>
+          <t>72,53; 96,61</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>46,83; 73,79</t>
+          <t>46,67; 73,96</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>57,27; 100,0</t>
+          <t>56,52; 100,0</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>59,73; 86,29</t>
+          <t>59,43; 86,58</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>61,9; 85,1</t>
+          <t>62,11; 85,27</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>54,76; 73,36</t>
+          <t>54,65; 73,62</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>56,65; 83,91</t>
+          <t>57,93; 83,91</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>64,33; 86,01</t>
+          <t>67,05; 87,37</t>
         </is>
       </c>
     </row>
@@ -1277,62 +1277,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>58,64; 100,0</t>
+          <t>66,51; 100,0</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>45,23; 81,73</t>
+          <t>41,79; 78,76</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>26,66; 69,09</t>
+          <t>24,9; 69,29</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>63,75; 100,0</t>
+          <t>65,81; 100,0</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>48,82; 87,22</t>
+          <t>48,31; 87,16</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>40,81; 77,81</t>
+          <t>40,71; 75,92</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>28,85; 80,53</t>
+          <t>28,76; 80,82</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>78,24; 100,0</t>
+          <t>79,22; 100,0</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>61,08; 89,57</t>
+          <t>63,49; 89,24</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>47,83; 73,41</t>
+          <t>47,69; 72,63</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>34,81; 68,41</t>
+          <t>33,42; 67,95</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>81,68; 98,5</t>
+          <t>79,85; 98,27</t>
         </is>
       </c>
     </row>
@@ -1417,12 +1417,12 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>23,75; 100,0</t>
+          <t>26,64; 100,0</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 74,71</t>
+          <t>0,0; 73,77</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
@@ -1432,47 +1432,47 @@
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>9,2; 100,0</t>
+          <t>17,78; 100,0</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>55,53; 100,0</t>
+          <t>49,4; 100,0</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>39,48; 100,0</t>
+          <t>46,42; 100,0</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>12,54; 72,61</t>
+          <t>18,06; 72,58</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>8,48; 73,44</t>
+          <t>8,33; 75,51</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>57,29; 94,76</t>
+          <t>55,05; 94,7</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>31,18; 81,83</t>
+          <t>34,17; 80,74</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>14,52; 65,23</t>
+          <t>14,54; 65,72</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>19,8; 72,45</t>
+          <t>20,84; 73,71</t>
         </is>
       </c>
     </row>
@@ -1557,62 +1557,62 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>61,51; 82,15</t>
+          <t>62,06; 81,86</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>53,87; 71,23</t>
+          <t>53,19; 71,2</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>37,91; 60,79</t>
+          <t>38,08; 61,64</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>70,86; 89,1</t>
+          <t>71,89; 89,06</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>73,48; 87,8</t>
+          <t>73,71; 87,83</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>53,97; 71,08</t>
+          <t>53,58; 70,71</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>44,81; 66,87</t>
+          <t>44,23; 67,59</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>65,69; 83,48</t>
+          <t>65,76; 83,52</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>72,16; 83,83</t>
+          <t>71,92; 83,65</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>57,6; 69,62</t>
+          <t>56,64; 68,87</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>44,24; 61,56</t>
+          <t>44,07; 61,54</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>71,04; 83,82</t>
+          <t>70,61; 83,14</t>
         </is>
       </c>
     </row>
@@ -1669,7 +1669,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores según si dicha enfermedad o dolencia continuada le ha afectado para realizar actividades como pasear, ir al cine, hacer deporte, etc (tasa de respuesta: 98,79%)</t>
+          <t>Menores según si dicha enfermedad o dolencia continuada le ha afectado para realizar actividades de ocio como pasear, ir al cine, hacer deporte, etc (tasa de respuesta: 98,79%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -1927,62 +1927,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>3883; 8557</t>
+          <t>3976; 8662</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>1887; 6030</t>
+          <t>2010; 6140</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>597; 4555</t>
+          <t>544; 4163</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>6185; 10095</t>
+          <t>6214; 10061</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>7349; 11474</t>
+          <t>7318; 11474</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>2822; 6833</t>
+          <t>3190; 6856</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>1304; 5461</t>
+          <t>1257; 5444</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>4093; 10612</t>
+          <t>4144; 10724</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>12773; 19221</t>
+          <t>13098; 19214</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>6233; 12238</t>
+          <t>6116; 12221</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>2907; 8521</t>
+          <t>2734; 8517</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>11870; 19554</t>
+          <t>11895; 19572</t>
         </is>
       </c>
     </row>
@@ -2135,12 +2135,12 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>2708; 7069</t>
+          <t>2401; 7069</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>4344; 8475</t>
+          <t>4507; 8475</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
@@ -2150,47 +2150,47 @@
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>3699; 7607</t>
+          <t>3497; 7609</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>3280; 7964</t>
+          <t>3305; 7985</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>1877; 6290</t>
+          <t>1861; 6262</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>1795; 6356</t>
+          <t>1750; 6503</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>6253; 10781</t>
+          <t>6226; 10760</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>8020; 14071</t>
+          <t>7933; 14099</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>7573; 13910</t>
+          <t>7620; 13916</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>1973; 7228</t>
+          <t>1965; 7255</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>12116; 18093</t>
+          <t>11300; 17812</t>
         </is>
       </c>
     </row>
@@ -2348,7 +2348,7 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>1299; 6021</t>
+          <t>1240; 6112</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
@@ -2363,42 +2363,42 @@
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>9801; 13871</t>
+          <t>9845; 13871</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>5759; 10853</t>
+          <t>5338; 10758</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>647; 4528</t>
+          <t>652; 4510</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>2958; 7315</t>
+          <t>3005; 7294</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>13043; 17714</t>
+          <t>13108; 17714</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>8380; 15985</t>
+          <t>7964; 15657</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>1732; 6397</t>
+          <t>1786; 6419</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>4826; 9825</t>
+          <t>5133; 9874</t>
         </is>
       </c>
     </row>
@@ -2551,62 +2551,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>7107; 13704</t>
+          <t>7127; 13417</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>18061; 27087</t>
+          <t>18232; 26792</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>7020; 13314</t>
+          <t>6775; 12994</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>15463; 23475</t>
+          <t>15607; 23354</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>13954; 19345</t>
+          <t>14522; 19345</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>17390; 27399</t>
+          <t>17329; 27463</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>6272; 10953</t>
+          <t>6190; 10953</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>18652; 26946</t>
+          <t>18559; 27037</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>23170; 31855</t>
+          <t>23252; 31921</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>38859; 52058</t>
+          <t>38783; 52243</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>15501; 22962</t>
+          <t>15851; 22961</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>36208; 48409</t>
+          <t>37735; 49176</t>
         </is>
       </c>
     </row>
@@ -2759,62 +2759,62 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>5130; 8749</t>
+          <t>5819; 8749</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>7855; 14194</t>
+          <t>7258; 13679</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>3666; 9500</t>
+          <t>3424; 9526</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>8300; 13020</t>
+          <t>8568; 13020</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>7572; 13526</t>
+          <t>7492; 13516</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>9236; 17612</t>
+          <t>9214; 17182</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>2858; 7980</t>
+          <t>2850; 8008</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>20731; 26496</t>
+          <t>20989; 26496</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>14818; 21727</t>
+          <t>15401; 21648</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>19134; 29363</t>
+          <t>19077; 29054</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>8235; 16184</t>
+          <t>7907; 16076</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>32276; 38922</t>
+          <t>31553; 38830</t>
         </is>
       </c>
     </row>
@@ -2967,12 +2967,12 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>1099; 4626</t>
+          <t>1232; 4626</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>0; 3687</t>
+          <t>0; 3640</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
@@ -2982,47 +2982,47 @@
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>376; 4089</t>
+          <t>727; 4089</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>4400; 7924</t>
+          <t>3915; 7924</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>2512; 6361</t>
+          <t>2952; 6361</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>897; 5192</t>
+          <t>1291; 5189</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>479; 4142</t>
+          <t>470; 4259</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>7190; 11893</t>
+          <t>6909; 11885</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>3522; 9244</t>
+          <t>3861; 9121</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>1458; 6553</t>
+          <t>1460; 6602</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>1926; 7049</t>
+          <t>2027; 7172</t>
         </is>
       </c>
     </row>
@@ -3175,62 +3175,62 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>32059; 42814</t>
+          <t>32345; 42665</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>42876; 56691</t>
+          <t>42333; 56669</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>16795; 26932</t>
+          <t>16872; 27308</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>45028; 56624</t>
+          <t>45687; 56596</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>56938; 68040</t>
+          <t>57120; 68058</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>50773; 66862</t>
+          <t>50400; 66520</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>22301; 33279</t>
+          <t>22013; 33638</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>63486; 80674</t>
+          <t>63547; 80711</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>93525; 108655</t>
+          <t>93210; 108426</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>100024; 120897</t>
+          <t>98370; 119610</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>41615; 57911</t>
+          <t>41456; 57885</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>113803; 134268</t>
+          <t>113100; 133182</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/IP09B02-Clase-trans_dic.xlsx
+++ b/data/trans_dic/IP09B02-Clase-trans_dic.xlsx
@@ -533,7 +533,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -541,7 +541,7 @@
       <c r="F1" s="3" t="n"/>
       <c r="G1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="H1" s="3" t="n"/>
@@ -649,42 +649,42 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>87,92%</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>72,01%</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>43,75%</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>53,58%</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
           <t>66,61%</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="H4" s="2" t="inlineStr">
         <is>
           <t>59,9%</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="I4" s="2" t="inlineStr">
         <is>
           <t>42,87%</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>81,95%</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>87,92%</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>72,01%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>43,75%</t>
-        </is>
-      </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>51,69%</t>
+          <t>81,07%</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -704,7 +704,7 @@
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>64,61%</t>
+          <t>66,14%</t>
         </is>
       </c>
     </row>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>40,62; 88,49</t>
+          <t>63,58; 100,0</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>29,55; 90,27</t>
+          <t>37,56; 91,32</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>10,15; 77,69</t>
+          <t>17,62; 72,7</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>58,5; 94,71</t>
+          <t>30,87; 77,15</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>63,78; 100,0</t>
+          <t>38,5; 87,2</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>42,56; 91,49</t>
+          <t>29,4; 89,67</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>16,81; 72,82</t>
+          <t>9,63; 77,96</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>29,05; 75,18</t>
+          <t>54,05; 94,76</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>61,6; 90,36</t>
+          <t>59,4; 90,11</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>42,78; 85,48</t>
+          <t>43,05; 85,0</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>21,3; 66,36</t>
+          <t>22,67; 66,76</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>47,79; 78,64</t>
+          <t>49,44; 79,98</t>
         </is>
       </c>
     </row>
@@ -789,42 +789,42 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>68,17%</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>48,23%</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>45,6%</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>82,75%</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
           <t>70,75%</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="H6" s="2" t="inlineStr">
         <is>
           <t>83,49%</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="I6" s="2" t="inlineStr">
         <is>
           <t>28,19%</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>74,57%</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>68,17%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>48,23%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>45,6%</t>
-        </is>
-      </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>82,68%</t>
+          <t>74,09%</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -844,7 +844,7 @@
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>79,26%</t>
+          <t>78,95%</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>31,16; 91,76</t>
+          <t>37,01; 90,84</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>53,19; 100,0</t>
+          <t>20,78; 74,72</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 100,0</t>
+          <t>22,11; 75,46</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>42,64; 92,78</t>
+          <t>55,23; 95,9</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>38,04; 91,92</t>
+          <t>32,35; 91,8</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>22,41; 75,39</t>
+          <t>50,34; 100,0</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>20,52; 76,23</t>
+          <t>0,0; 79,19</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>55,38; 95,71</t>
+          <t>41,54; 93,56</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>48,4; 86,01</t>
+          <t>47,26; 85,96</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>45,41; 82,93</t>
+          <t>45,71; 82,6</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>17,71; 65,38</t>
+          <t>18,5; 65,6</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>58,12; 91,6</t>
+          <t>59,56; 91,3</t>
         </is>
       </c>
     </row>
@@ -929,44 +929,44 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>90,59%</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>71,19%</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>45,05%</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>70,8%</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="H8" s="2" t="inlineStr">
         <is>
           <t>41,74%</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
+      <c r="I8" s="2" t="inlineStr">
         <is>
           <t>37,15%</t>
         </is>
       </c>
-      <c r="F8" s="2" t="inlineStr">
+      <c r="J8" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>90,59%</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>71,19%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>45,05%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>70,66%</t>
-        </is>
-      </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
           <t>92,63%</t>
@@ -984,7 +984,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>77,94%</t>
+          <t>78,46%</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>70,78; 100,0</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>46,17; 89,1</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>11,37; 79,22</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>32,47; 94,08</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
           <t>—; —</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>15,16; 74,71</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>17,51; 69,05</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
         <is>
           <t>0,0; 81,95</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="J9" s="2" t="inlineStr">
         <is>
           <t>—; —</t>
         </is>
       </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>70,98; 100,0</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>43,95; 88,58</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>11,34; 78,51</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>38,69; 93,9</t>
-        </is>
-      </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>74,0; 100,0</t>
+          <t>76,78; 100,0</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>39,18; 77,03</t>
+          <t>39,98; 76,51</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>19,7; 70,8</t>
+          <t>15,3; 68,85</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>49,7; 95,59</t>
+          <t>44,99; 95,99</t>
         </is>
       </c>
     </row>
@@ -1069,42 +1069,42 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>86,64%</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>61,68%</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>85,31%</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>74,86%</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
           <t>61,0%</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="H10" s="2" t="inlineStr">
         <is>
           <t>67,62%</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
+      <c r="I10" s="2" t="inlineStr">
         <is>
           <t>62,74%</t>
         </is>
       </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>80,73%</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>86,64%</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>61,68%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>85,31%</t>
-        </is>
-      </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>74,94%</t>
+          <t>76,09%</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1124,7 +1124,7 @@
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>77,52%</t>
+          <t>75,38%</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>40,93; 77,07</t>
+          <t>70,0; 96,63</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>53,89; 79,2</t>
+          <t>48,92; 74,87</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>41,28; 79,18</t>
+          <t>57,37; 100,0</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>62,29; 93,21</t>
+          <t>59,56; 85,62</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>72,53; 96,61</t>
+          <t>41,53; 77,67</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>46,67; 73,96</t>
+          <t>54,43; 79,8</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>56,52; 100,0</t>
+          <t>43,32; 79,4</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>59,43; 86,58</t>
+          <t>54,73; 89,67</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>62,11; 85,27</t>
+          <t>61,86; 84,43</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>54,65; 73,62</t>
+          <t>55,17; 72,91</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>57,93; 83,91</t>
+          <t>56,71; 84,49</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>67,05; 87,37</t>
+          <t>63,52; 84,84</t>
         </is>
       </c>
     </row>
@@ -1209,42 +1209,42 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>70,05%</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>59,46%</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>58,39%</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>92,88%</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
           <t>91,62%</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="H12" s="2" t="inlineStr">
         <is>
           <t>63,31%</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="I12" s="2" t="inlineStr">
         <is>
           <t>47,96%</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>88,38%</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>70,05%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>59,46%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>58,39%</t>
-        </is>
-      </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>93,47%</t>
+          <t>87,91%</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
@@ -1264,7 +1264,7 @@
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>91,79%</t>
+          <t>91,1%</t>
         </is>
       </c>
     </row>
@@ -1277,62 +1277,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>66,51; 100,0</t>
+          <t>48,9; 87,2</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>41,79; 78,76</t>
+          <t>39,88; 75,36</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>24,9; 69,29</t>
+          <t>33,55; 81,69</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>65,81; 100,0</t>
+          <t>74,9; 99,18</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>48,31; 87,16</t>
+          <t>60,59; 100,0</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>40,71; 75,92</t>
+          <t>43,75; 81,14</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>28,76; 80,82</t>
+          <t>24,84; 69,38</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>79,22; 100,0</t>
+          <t>65,42; 100,0</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>63,49; 89,24</t>
+          <t>62,16; 89,06</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>47,69; 72,63</t>
+          <t>47,07; 73,18</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>33,42; 67,95</t>
+          <t>35,44; 68,52</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>79,85; 98,27</t>
+          <t>78,78; 97,62</t>
         </is>
       </c>
     </row>
@@ -1349,42 +1349,42 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>82,63%</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>78,93%</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>40,8%</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>38,53%</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
           <t>78,68%</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="H14" s="2" t="inlineStr">
         <is>
           <t>30,36%</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
+      <c r="I14" s="2" t="inlineStr">
         <is>
           <t>27,35%</t>
         </is>
       </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>59,32%</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>82,63%</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>78,93%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>40,8%</t>
-        </is>
-      </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>38,52%</t>
+          <t>63,39%</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -1404,7 +1404,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>47,26%</t>
+          <t>49,55%</t>
         </is>
       </c>
     </row>
@@ -1417,62 +1417,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>26,64; 100,0</t>
+          <t>56,34; 100,0</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 73,77</t>
+          <t>40,0; 100,0</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 100,0</t>
+          <t>11,67; 72,35</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>17,78; 100,0</t>
+          <t>7,26; 78,98</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>49,4; 100,0</t>
+          <t>26,0; 100,0</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>46,42; 100,0</t>
+          <t>0,0; 74,92</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>18,06; 72,58</t>
+          <t>0,0; 83,7</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>8,33; 75,51</t>
+          <t>17,31; 100,0</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>55,05; 94,7</t>
+          <t>57,11; 94,7</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>34,17; 80,74</t>
+          <t>31,73; 81,06</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>14,54; 65,72</t>
+          <t>14,64; 65,68</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>20,84; 73,71</t>
+          <t>21,69; 76,24</t>
         </is>
       </c>
     </row>
@@ -1489,42 +1489,42 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>81,74%</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>63,17%</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>55,85%</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>74,81%</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
           <t>73,08%</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="H16" s="2" t="inlineStr">
         <is>
           <t>62,74%</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
+      <c r="I16" s="2" t="inlineStr">
         <is>
           <t>49,52%</t>
         </is>
       </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>81,1%</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>81,74%</t>
-        </is>
-      </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>63,17%</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>55,85%</t>
-        </is>
-      </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>75,02%</t>
+          <t>79,28%</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr">
@@ -1544,7 +1544,7 @@
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>77,43%</t>
+          <t>76,62%</t>
         </is>
       </c>
     </row>
@@ -1557,62 +1557,62 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>62,06; 81,86</t>
+          <t>73,35; 87,85</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>53,19; 71,2</t>
+          <t>54,71; 71,19</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>38,08; 61,64</t>
+          <t>44,64; 67,61</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>71,89; 89,06</t>
+          <t>65,49; 83,06</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>73,71; 87,83</t>
+          <t>60,8; 82,02</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>53,58; 70,71</t>
+          <t>52,75; 70,14</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>44,23; 67,59</t>
+          <t>36,08; 61,38</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>65,76; 83,52</t>
+          <t>69,21; 86,74</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>71,92; 83,65</t>
+          <t>72,37; 84,35</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>56,64; 68,87</t>
+          <t>56,96; 68,89</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>44,07; 61,54</t>
+          <t>43,76; 60,94</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>70,61; 83,14</t>
+          <t>70,16; 82,62</t>
         </is>
       </c>
     </row>
@@ -1675,7 +1675,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -1683,7 +1683,7 @@
       <c r="F1" s="3" t="n"/>
       <c r="G1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="H1" s="3" t="n"/>
@@ -1791,42 +1791,42 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
           <t>10</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="H4" s="2" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="I4" s="2" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
+      <c r="J4" s="2" t="inlineStr">
         <is>
           <t>13</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>8</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -1859,42 +1859,42 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>10088</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>5396</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>3271</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>6861</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
           <t>6521</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="H5" s="2" t="inlineStr">
         <is>
           <t>4075</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
+      <c r="I5" s="2" t="inlineStr">
         <is>
           <t>2297</t>
         </is>
       </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>8706</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>10088</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>5396</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>3271</t>
-        </is>
-      </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>7372</t>
+          <t>8731</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -1914,7 +1914,7 @@
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>16079</t>
+          <t>15593</t>
         </is>
       </c>
     </row>
@@ -1927,62 +1927,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>3976; 8662</t>
+          <t>7295; 11474</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>2010; 6140</t>
+          <t>2815; 6844</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>544; 4163</t>
+          <t>1317; 5435</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>6214; 10061</t>
+          <t>3953; 9880</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>7318; 11474</t>
+          <t>3768; 8536</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>3190; 6856</t>
+          <t>2000; 6099</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>1257; 5444</t>
+          <t>516; 4177</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>4144; 10724</t>
+          <t>5821; 10206</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>13098; 19214</t>
+          <t>12632; 19160</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>6116; 12221</t>
+          <t>6155; 12151</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>2734; 8517</t>
+          <t>2910; 8568</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>11895; 19572</t>
+          <t>11656; 18855</t>
         </is>
       </c>
     </row>
@@ -1999,42 +1999,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
           <t>8</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="H7" s="2" t="inlineStr">
         <is>
           <t>11</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
+      <c r="I7" s="2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="F7" s="2" t="inlineStr">
+      <c r="J7" s="2" t="inlineStr">
         <is>
           <t>9</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>12</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
@@ -2067,42 +2067,42 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>5922</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>4006</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>3891</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>8970</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
           <t>5451</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="H8" s="2" t="inlineStr">
         <is>
           <t>7076</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
+      <c r="I8" s="2" t="inlineStr">
         <is>
           <t>724</t>
         </is>
       </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>6116</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>5922</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>4006</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>3891</t>
-        </is>
-      </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>9295</t>
+          <t>6268</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -2122,7 +2122,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>15411</t>
+          <t>15238</t>
         </is>
       </c>
     </row>
@@ -2135,62 +2135,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>2401; 7069</t>
+          <t>3215; 7892</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>4507; 8475</t>
+          <t>1726; 6206</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0; 2567</t>
+          <t>1886; 6438</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>3497; 7609</t>
+          <t>5987; 10396</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>3305; 7985</t>
+          <t>2492; 7072</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>1861; 6262</t>
+          <t>4267; 8475</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>1750; 6503</t>
+          <t>0; 2033</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>6226; 10760</t>
+          <t>3514; 7916</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>7933; 14099</t>
+          <t>7746; 14090</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>7620; 13916</t>
+          <t>7671; 13861</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>1965; 7255</t>
+          <t>2053; 7280</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>11300; 17812</t>
+          <t>11495; 17620</t>
         </is>
       </c>
     </row>
@@ -2207,42 +2207,42 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
           <t>6</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="H10" s="2" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
+      <c r="I10" s="2" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="F10" s="2" t="inlineStr">
+      <c r="J10" s="2" t="inlineStr">
         <is>
           <t>4</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>18</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>8</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -2275,42 +2275,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>12566</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>8646</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>2588</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>4767</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
           <t>3842</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="H11" s="2" t="inlineStr">
         <is>
           <t>3415</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
+      <c r="I11" s="2" t="inlineStr">
         <is>
           <t>1234</t>
         </is>
       </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>2560</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>12566</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>8646</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>2588</t>
-        </is>
-      </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>5489</t>
+          <t>2395</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
@@ -2330,7 +2330,7 @@
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>8050</t>
+          <t>7162</t>
         </is>
       </c>
     </row>
@@ -2343,62 +2343,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>9818; 13871</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>5607; 10822</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>653; 4551</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>2187; 6336</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
           <t>—; —</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>1240; 6112</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>1433; 5650</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
         <is>
           <t>0; 2723</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
+      <c r="J12" s="2" t="inlineStr">
         <is>
           <t>—; —</t>
         </is>
       </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>9845; 13871</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>5338; 10758</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>652; 4510</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>3005; 7294</t>
-        </is>
-      </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>13108; 17714</t>
+          <t>13600; 17714</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>7964; 15657</t>
+          <t>8127; 15552</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>1786; 6419</t>
+          <t>1387; 6243</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>5133; 9874</t>
+          <t>4106; 8762</t>
         </is>
       </c>
     </row>
@@ -2415,42 +2415,42 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>31</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>29</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
           <t>16</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="H13" s="2" t="inlineStr">
         <is>
           <t>33</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
+      <c r="I13" s="2" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="F13" s="2" t="inlineStr">
+      <c r="J13" s="2" t="inlineStr">
         <is>
           <t>24</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>26</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>31</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>14</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>29</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
@@ -2483,42 +2483,42 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>17350</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>22903</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>9343</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>20858</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
           <t>10620</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="H14" s="2" t="inlineStr">
         <is>
           <t>22875</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
+      <c r="I14" s="2" t="inlineStr">
         <is>
           <t>10297</t>
         </is>
       </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>20226</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>17350</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>22903</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>9343</t>
-        </is>
-      </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>23401</t>
+          <t>15400</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -2538,7 +2538,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>43628</t>
+          <t>36257</t>
         </is>
       </c>
     </row>
@@ -2551,62 +2551,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>7127; 13417</t>
+          <t>14016; 19349</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>18232; 26792</t>
+          <t>18166; 27800</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>6775; 12994</t>
+          <t>6284; 10953</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>15607; 23354</t>
+          <t>16595; 23855</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>14522; 19345</t>
+          <t>7231; 13522</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>17329; 27463</t>
+          <t>18411; 26996</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>6190; 10953</t>
+          <t>7109; 13031</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>18559; 27037</t>
+          <t>11076; 18148</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>23252; 31921</t>
+          <t>23155; 31607</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>38783; 52243</t>
+          <t>39151; 51741</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>15851; 22961</t>
+          <t>15519; 23121</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>37735; 49176</t>
+          <t>30554; 40809</t>
         </is>
       </c>
     </row>
@@ -2623,42 +2623,42 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
           <t>12</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="H16" s="2" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
+      <c r="I16" s="2" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="F16" s="2" t="inlineStr">
+      <c r="J16" s="2" t="inlineStr">
         <is>
           <t>17</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>19</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>18</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr">
@@ -2691,42 +2691,42 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>10863</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>13457</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>5786</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>21258</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
           <t>8016</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="H17" s="2" t="inlineStr">
         <is>
           <t>10996</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
+      <c r="I17" s="2" t="inlineStr">
         <is>
           <t>6594</t>
         </is>
       </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>11507</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
-        <is>
-          <t>10863</t>
-        </is>
-      </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>13457</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>5786</t>
-        </is>
-      </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>24766</t>
+          <t>11234</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
@@ -2746,7 +2746,7 @@
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>36272</t>
+          <t>32493</t>
         </is>
       </c>
     </row>
@@ -2759,62 +2759,62 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>5819; 8749</t>
+          <t>7584; 13523</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>7258; 13679</t>
+          <t>9025; 17056</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>3424; 9526</t>
+          <t>3325; 8095</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>8568; 13020</t>
+          <t>17143; 22700</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>7492; 13516</t>
+          <t>5301; 8749</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>9214; 17182</t>
+          <t>7598; 14092</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>2850; 8008</t>
+          <t>3415; 9540</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>20989; 26496</t>
+          <t>8360; 12779</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>15401; 21648</t>
+          <t>15079; 21604</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>19077; 29054</t>
+          <t>18828; 29273</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>7907; 16076</t>
+          <t>8385; 16210</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>31553; 38830</t>
+          <t>28099; 34820</t>
         </is>
       </c>
     </row>
@@ -2831,42 +2831,42 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="D19" s="2" t="inlineStr">
+      <c r="H19" s="2" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="E19" s="2" t="inlineStr">
+      <c r="I19" s="2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="F19" s="2" t="inlineStr">
+      <c r="J19" s="2" t="inlineStr">
         <is>
           <t>4</t>
-        </is>
-      </c>
-      <c r="G19" s="2" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="H19" s="2" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="I19" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="J19" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
@@ -2899,42 +2899,42 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
+          <t>6548</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>5021</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>2917</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>2149</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
           <t>3640</t>
         </is>
       </c>
-      <c r="D20" s="2" t="inlineStr">
+      <c r="H20" s="2" t="inlineStr">
         <is>
           <t>1498</t>
         </is>
       </c>
-      <c r="E20" s="2" t="inlineStr">
+      <c r="I20" s="2" t="inlineStr">
         <is>
           <t>792</t>
         </is>
       </c>
-      <c r="F20" s="2" t="inlineStr">
-        <is>
-          <t>2425</t>
-        </is>
-      </c>
-      <c r="G20" s="2" t="inlineStr">
-        <is>
-          <t>6548</t>
-        </is>
-      </c>
-      <c r="H20" s="2" t="inlineStr">
-        <is>
-          <t>5021</t>
-        </is>
-      </c>
-      <c r="I20" s="2" t="inlineStr">
-        <is>
-          <t>2917</t>
-        </is>
-      </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t>2172</t>
+          <t>2814</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr">
@@ -2954,7 +2954,7 @@
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>4598</t>
+          <t>4963</t>
         </is>
       </c>
     </row>
@@ -2967,62 +2967,62 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>1232; 4626</t>
+          <t>4464; 7924</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>0; 3640</t>
+          <t>2545; 6361</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>0; 2895</t>
+          <t>835; 5173</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>727; 4089</t>
+          <t>405; 4404</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>3915; 7924</t>
+          <t>1203; 4626</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>2952; 6361</t>
+          <t>0; 3698</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>1291; 5189</t>
+          <t>0; 2423</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>470; 4259</t>
+          <t>769; 4440</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>6909; 11885</t>
+          <t>7167; 11885</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>3861; 9121</t>
+          <t>3585; 9157</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>1460; 6602</t>
+          <t>1471; 6598</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>2027; 7172</t>
+          <t>2172; 7636</t>
         </is>
       </c>
     </row>
@@ -3039,42 +3039,42 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
+          <t>94</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>84</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
+          <t>78</t>
+        </is>
+      </c>
+      <c r="G22" s="2" t="inlineStr">
+        <is>
           <t>57</t>
         </is>
       </c>
-      <c r="D22" s="2" t="inlineStr">
+      <c r="H22" s="2" t="inlineStr">
         <is>
           <t>72</t>
         </is>
       </c>
-      <c r="E22" s="2" t="inlineStr">
+      <c r="I22" s="2" t="inlineStr">
         <is>
           <t>33</t>
         </is>
       </c>
-      <c r="F22" s="2" t="inlineStr">
+      <c r="J22" s="2" t="inlineStr">
         <is>
           <t>71</t>
-        </is>
-      </c>
-      <c r="G22" s="2" t="inlineStr">
-        <is>
-          <t>94</t>
-        </is>
-      </c>
-      <c r="H22" s="2" t="inlineStr">
-        <is>
-          <t>84</t>
-        </is>
-      </c>
-      <c r="I22" s="2" t="inlineStr">
-        <is>
-          <t>40</t>
-        </is>
-      </c>
-      <c r="J22" s="2" t="inlineStr">
-        <is>
-          <t>78</t>
         </is>
       </c>
       <c r="K22" s="2" t="inlineStr">
@@ -3107,42 +3107,42 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
+          <t>63337</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>59430</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>27796</t>
+        </is>
+      </c>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
+          <t>64863</t>
+        </is>
+      </c>
+      <c r="G23" s="2" t="inlineStr">
+        <is>
           <t>38088</t>
         </is>
       </c>
-      <c r="D23" s="2" t="inlineStr">
+      <c r="H23" s="2" t="inlineStr">
         <is>
           <t>49935</t>
         </is>
       </c>
-      <c r="E23" s="2" t="inlineStr">
+      <c r="I23" s="2" t="inlineStr">
         <is>
           <t>21937</t>
         </is>
       </c>
-      <c r="F23" s="2" t="inlineStr">
-        <is>
-          <t>51540</t>
-        </is>
-      </c>
-      <c r="G23" s="2" t="inlineStr">
-        <is>
-          <t>63337</t>
-        </is>
-      </c>
-      <c r="H23" s="2" t="inlineStr">
-        <is>
-          <t>59430</t>
-        </is>
-      </c>
-      <c r="I23" s="2" t="inlineStr">
-        <is>
-          <t>27796</t>
-        </is>
-      </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>72496</t>
+          <t>46842</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
@@ -3162,7 +3162,7 @@
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>124037</t>
+          <t>111705</t>
         </is>
       </c>
     </row>
@@ -3175,62 +3175,62 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>32345; 42665</t>
+          <t>56841; 68074</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>42333; 56669</t>
+          <t>51462; 66972</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>16872; 27308</t>
+          <t>22216; 33648</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>45687; 56596</t>
+          <t>56780; 72020</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>57120; 68058</t>
+          <t>31690; 42748</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>50400; 66520</t>
+          <t>41987; 55825</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>22013; 33638</t>
+          <t>15987; 27193</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>63547; 80711</t>
+          <t>40889; 51248</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>93210; 108426</t>
+          <t>93798; 109331</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>98370; 119610</t>
+          <t>98924; 119635</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>41456; 57885</t>
+          <t>41166; 57329</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>113100; 133182</t>
+          <t>102284; 120442</t>
         </is>
       </c>
     </row>
